--- a/output/shocapp_ordini_settimanali_for_pdf.xlsx
+++ b/output/shocapp_ordini_settimanali_for_pdf.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" s="9" t="inlineStr">
         <is>
@@ -615,30 +615,32 @@
         </is>
       </c>
       <c r="B3" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>CHEESECAKE MIRTILLI</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>CHEESECAKE MIRTILLI</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="n">
-        <v>2</v>
-      </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
           <t>CIOCCOLATO AL LATTE GELATO</t>
         </is>
       </c>
       <c r="F3" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
           <t>AMARENA</t>
         </is>
       </c>
-      <c r="H3" s="10" t="str"/>
+      <c r="H3" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -756,7 +758,9 @@
           <t>BANANA E LIME</t>
         </is>
       </c>
-      <c r="H7" s="10" t="str"/>
+      <c r="H7" s="10" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
@@ -765,7 +769,7 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
@@ -779,14 +783,16 @@
         </is>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
           <t>CACHI</t>
         </is>
       </c>
-      <c r="H8" s="10" t="str"/>
+      <c r="H8" s="10" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
@@ -848,7 +854,9 @@
           <t>FINOCCHIO MIELE LIQUIRIZIA</t>
         </is>
       </c>
-      <c r="B11" s="10" t="str"/>
+      <c r="B11" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
           <t>LEMON CURD</t>
@@ -969,7 +977,7 @@
         </is>
       </c>
       <c r="F15" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
@@ -1025,14 +1033,16 @@
         </is>
       </c>
       <c r="F17" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
           <t>FRAGOLA</t>
         </is>
       </c>
-      <c r="H17" s="10" t="str"/>
+      <c r="H17" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
@@ -1054,7 +1064,9 @@
           <t>FIOR DI CIOCCOLATO</t>
         </is>
       </c>
-      <c r="F18" s="10" t="str"/>
+      <c r="F18" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
           <t>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</t>
@@ -1162,7 +1174,9 @@
           <t>SACHER TORTE</t>
         </is>
       </c>
-      <c r="F22" s="10" t="str"/>
+      <c r="F22" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
           <t>LAMPONI SORBETTO</t>
@@ -1178,7 +1192,9 @@
           <t>NOCCIOLA</t>
         </is>
       </c>
-      <c r="B23" s="10" t="str"/>
+      <c r="B23" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
           <t>FIORI DI MAGNOLIA &amp; LIME</t>
@@ -1311,7 +1327,7 @@
         </is>
       </c>
       <c r="B28" s="10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
@@ -1339,7 +1355,7 @@
         </is>
       </c>
       <c r="B29" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
@@ -1368,7 +1384,9 @@
           <t>POLLICINA</t>
         </is>
       </c>
-      <c r="B30" s="10" t="str"/>
+      <c r="B30" s="10" t="n">
+        <v>2</v>
+      </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
           <t>NON TI SCORDAR DI ME</t>
@@ -1394,7 +1412,9 @@
           <t>RICOTTA E AGRUMI</t>
         </is>
       </c>
-      <c r="B31" s="10" t="str"/>
+      <c r="B31" s="10" t="n">
+        <v>2</v>
+      </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
           <t>PASTIERA NAPOLETANA</t>
@@ -1464,7 +1484,9 @@
           <t>PASSION FRUIT</t>
         </is>
       </c>
-      <c r="H33" s="10" t="str"/>
+      <c r="H33" s="10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="9" t="inlineStr">
@@ -1645,7 +1667,7 @@
         </is>
       </c>
       <c r="B40" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
@@ -1672,7 +1694,9 @@
           <t>TE VERDE MATCHA</t>
         </is>
       </c>
-      <c r="B41" s="10" t="str"/>
+      <c r="B41" s="10" t="n">
+        <v>1</v>
+      </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
           <t>TORRONE SALATO</t>
@@ -1821,7 +1845,7 @@
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>Totale vaschette: 81</t>
+          <t>Totale vaschette: 118</t>
         </is>
       </c>
       <c r="B49" s="10" t="n"/>
